--- a/sources/yoshimitsu_step8.xlsx
+++ b/sources/yoshimitsu_step8.xlsx
@@ -7490,12 +7490,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>ms[!]</t>
+          <t>ms!</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>[!]h</t>
+          <t>!h</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>[!]m</t>
+          <t>!m</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -10993,12 +10993,12 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>[!]-[!]</t>
+          <t>!-!</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">

--- a/sources/yoshimitsu_step8.xlsx
+++ b/sources/yoshimitsu_step8.xlsx
@@ -851,6 +851,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -913,6 +918,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -973,6 +983,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -11668,6 +11683,11 @@
           <t>hmmhhLm!!!</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="Z134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -11715,6 +11735,11 @@
           <t>hmmhmmmm!!</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="Z135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -11762,6 +11787,11 @@
           <t>hhmhhLm!!!</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="Z136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -11809,6 +11839,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="Z137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -11856,6 +11891,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="Z138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -11903,6 +11943,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="Z139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -11948,6 +11993,11 @@
       <c r="S140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
